--- a/artfynd/A 33004-2026 artfynd.xlsx
+++ b/artfynd/A 33004-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62590568</v>
+        <v>136667964</v>
       </c>
       <c r="B2" t="n">
-        <v>101326</v>
+        <v>92663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>3884</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skogstorp Ö, Srm</t>
+          <t>Skogstorp, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585112</v>
+        <v>585135</v>
       </c>
       <c r="R2" t="n">
-        <v>6577321</v>
+        <v>6577401</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +752,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-11-23</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-11-23</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Växer på död stam av hassel</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,28 +787,1047 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136667964</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136669325</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58003</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Skogstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>585098</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6577297</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136669325</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136668544</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56737</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skogstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>585047</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6577324</v>
+      </c>
+      <c r="S4" t="n">
+        <v>11</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ko med två kalvar</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136668544</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136668377</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58843</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skogstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>585137</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6577366</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136668377</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136668478</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58843</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skogstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>585122</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6577337</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136668478</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136668606</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58843</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skogstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>585009</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6577320</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136668606</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136669407</v>
+      </c>
+      <c r="B8" t="n">
+        <v>104865</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skogstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>585018</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6577342</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136669407</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>62590568</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skogstorp Ö, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>585112</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6577321</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2016-11-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2016-11-23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Caspar Ström</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Caspar Ström</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY9" t="inlineStr">
         <is>
           <t>Stadens biologiska mångfald (LONA)</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/62590568</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136667440</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101552</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skogstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>585177</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6577418</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Växer ymnigt på skogsmarken</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136667440</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33004-2026 artfynd.xlsx
+++ b/artfynd/A 33004-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136667964</v>
       </c>
       <c r="B2" t="n">
-        <v>92663</v>
+        <v>92666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>136669407</v>
       </c>
       <c r="B8" t="n">
-        <v>104865</v>
+        <v>104868</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136667440</v>
       </c>
       <c r="B10" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33004-2026 artfynd.xlsx
+++ b/artfynd/A 33004-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136667964</v>
       </c>
       <c r="B2" t="n">
-        <v>92666</v>
+        <v>92667</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>136669407</v>
       </c>
       <c r="B8" t="n">
-        <v>104868</v>
+        <v>104869</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136667440</v>
       </c>
       <c r="B10" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33004-2026 artfynd.xlsx
+++ b/artfynd/A 33004-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136667964</v>
       </c>
       <c r="B2" t="n">
-        <v>92667</v>
+        <v>92672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>136669325</v>
       </c>
       <c r="B3" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>136668544</v>
       </c>
       <c r="B4" t="n">
-        <v>56737</v>
+        <v>56739</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         <v>136668377</v>
       </c>
       <c r="B5" t="n">
-        <v>58843</v>
+        <v>58845</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>136668478</v>
       </c>
       <c r="B6" t="n">
-        <v>58843</v>
+        <v>58845</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>136668606</v>
       </c>
       <c r="B7" t="n">
-        <v>58843</v>
+        <v>58845</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>136669407</v>
       </c>
       <c r="B8" t="n">
-        <v>104869</v>
+        <v>104874</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136667440</v>
       </c>
       <c r="B10" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33004-2026 artfynd.xlsx
+++ b/artfynd/A 33004-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136667964</v>
       </c>
       <c r="B2" t="n">
-        <v>92672</v>
+        <v>92674</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>136669407</v>
       </c>
       <c r="B8" t="n">
-        <v>104874</v>
+        <v>104876</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136667440</v>
       </c>
       <c r="B10" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33004-2026 artfynd.xlsx
+++ b/artfynd/A 33004-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136667964</v>
       </c>
       <c r="B2" t="n">
-        <v>92674</v>
+        <v>92676</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>136669407</v>
       </c>
       <c r="B8" t="n">
-        <v>104876</v>
+        <v>104882</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136667440</v>
       </c>
       <c r="B10" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33004-2026 artfynd.xlsx
+++ b/artfynd/A 33004-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136667964</v>
       </c>
       <c r="B2" t="n">
-        <v>92676</v>
+        <v>92678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>136669407</v>
       </c>
       <c r="B8" t="n">
-        <v>104882</v>
+        <v>104884</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136667440</v>
       </c>
       <c r="B10" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33004-2026 artfynd.xlsx
+++ b/artfynd/A 33004-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136667964</v>
       </c>
       <c r="B2" t="n">
-        <v>92678</v>
+        <v>92679</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>136669407</v>
       </c>
       <c r="B8" t="n">
-        <v>104884</v>
+        <v>104885</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136667440</v>
       </c>
       <c r="B10" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33004-2026 artfynd.xlsx
+++ b/artfynd/A 33004-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136667964</v>
       </c>
       <c r="B2" t="n">
-        <v>92679</v>
+        <v>92685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>136669407</v>
       </c>
       <c r="B8" t="n">
-        <v>104885</v>
+        <v>104891</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136667440</v>
       </c>
       <c r="B10" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33004-2026 artfynd.xlsx
+++ b/artfynd/A 33004-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136667964</v>
       </c>
       <c r="B2" t="n">
-        <v>92685</v>
+        <v>92689</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>136669407</v>
       </c>
       <c r="B8" t="n">
-        <v>104891</v>
+        <v>104895</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136667440</v>
       </c>
       <c r="B10" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33004-2026 artfynd.xlsx
+++ b/artfynd/A 33004-2026 artfynd.xlsx
@@ -1459,7 +1459,7 @@
         <v>136669407</v>
       </c>
       <c r="B8" t="n">
-        <v>104895</v>
+        <v>104897</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136667440</v>
       </c>
       <c r="B10" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33004-2026 artfynd.xlsx
+++ b/artfynd/A 33004-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136667964</v>
       </c>
       <c r="B2" t="n">
-        <v>92689</v>
+        <v>92691</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>136669407</v>
       </c>
       <c r="B8" t="n">
-        <v>104897</v>
+        <v>104899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136667440</v>
       </c>
       <c r="B10" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33004-2026 artfynd.xlsx
+++ b/artfynd/A 33004-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136667964</v>
       </c>
       <c r="B2" t="n">
-        <v>92691</v>
+        <v>92704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>136669325</v>
       </c>
       <c r="B3" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>136668544</v>
       </c>
       <c r="B4" t="n">
-        <v>56739</v>
+        <v>56752</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         <v>136668377</v>
       </c>
       <c r="B5" t="n">
-        <v>58845</v>
+        <v>58858</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>136668478</v>
       </c>
       <c r="B6" t="n">
-        <v>58845</v>
+        <v>58858</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>136668606</v>
       </c>
       <c r="B7" t="n">
-        <v>58845</v>
+        <v>58858</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>136669407</v>
       </c>
       <c r="B8" t="n">
-        <v>104899</v>
+        <v>104912</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136667440</v>
       </c>
       <c r="B10" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33004-2026 artfynd.xlsx
+++ b/artfynd/A 33004-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136667964</v>
       </c>
       <c r="B2" t="n">
-        <v>92704</v>
+        <v>92706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>136669325</v>
       </c>
       <c r="B3" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>136668544</v>
       </c>
       <c r="B4" t="n">
-        <v>56752</v>
+        <v>56754</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         <v>136668377</v>
       </c>
       <c r="B5" t="n">
-        <v>58858</v>
+        <v>58860</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>136668478</v>
       </c>
       <c r="B6" t="n">
-        <v>58858</v>
+        <v>58860</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>136668606</v>
       </c>
       <c r="B7" t="n">
-        <v>58858</v>
+        <v>58860</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>136669407</v>
       </c>
       <c r="B8" t="n">
-        <v>104912</v>
+        <v>104914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136667440</v>
       </c>
       <c r="B10" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33004-2026 artfynd.xlsx
+++ b/artfynd/A 33004-2026 artfynd.xlsx
@@ -837,17 +837,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -971,11 +963,7 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1105,11 +1093,7 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1234,11 +1218,7 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1363,11 +1343,7 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>observerad</t>

--- a/artfynd/A 33004-2026 artfynd.xlsx
+++ b/artfynd/A 33004-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136667964</v>
       </c>
       <c r="B2" t="n">
-        <v>92706</v>
+        <v>92709</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>136669407</v>
       </c>
       <c r="B8" t="n">
-        <v>104914</v>
+        <v>104917</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>136667440</v>
       </c>
       <c r="B10" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33004-2026 artfynd.xlsx
+++ b/artfynd/A 33004-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,35 +680,39 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136667964</v>
+        <v>137306078</v>
       </c>
       <c r="B2" t="n">
-        <v>92709</v>
+        <v>92958</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3884</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -722,13 +726,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585135</v>
+        <v>585178</v>
       </c>
       <c r="R2" t="n">
-        <v>6577401</v>
+        <v>6577342</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,27 +756,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:41</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Växer på död stam av hassel</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,33 +770,54 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136667964</t>
+          <t>https://artportalen.se/Sighting/137306078</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136669325</v>
+        <v>136667964</v>
       </c>
       <c r="B3" t="n">
-        <v>58020</v>
+        <v>92709</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,49 +825,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>3884</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skogstorp, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585098</v>
+        <v>585135</v>
       </c>
       <c r="R3" t="n">
-        <v>6577297</v>
+        <v>6577401</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,7 +891,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +901,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Växer på död stam av hassel</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,66 +932,54 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136669325</t>
+          <t>https://artportalen.se/Sighting/136667964</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136668544</v>
+        <v>137312651</v>
       </c>
       <c r="B4" t="n">
-        <v>56754</v>
+        <v>92719</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>206046</v>
+        <v>3884</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skogstorp, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585047</v>
+        <v>585166</v>
       </c>
       <c r="R4" t="n">
-        <v>6577324</v>
+        <v>6577415</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1005,27 +1003,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ko med två kalvar</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,31 +1029,51 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Högörtblandskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136668544</t>
+          <t>https://artportalen.se/Sighting/137312651</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136668377</v>
+        <v>136669325</v>
       </c>
       <c r="B5" t="n">
-        <v>58860</v>
+        <v>58020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,16 +1081,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208245</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1090,7 +1103,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -1105,13 +1117,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585137</v>
+        <v>585098</v>
       </c>
       <c r="R5" t="n">
-        <v>6577366</v>
+        <v>6577297</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1140,7 +1152,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1150,7 +1162,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1176,16 +1188,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136668377</t>
+          <t>https://artportalen.se/Sighting/136669325</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136668478</v>
+        <v>137306085</v>
       </c>
       <c r="B6" t="n">
-        <v>58860</v>
+        <v>58030</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,16 +1205,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208245</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1210,33 +1222,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skogstorp, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585122</v>
+        <v>584993</v>
       </c>
       <c r="R6" t="n">
-        <v>6577337</v>
+        <v>6577371</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1260,22 +1263,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1286,31 +1279,36 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136668478</t>
+          <t>https://artportalen.se/Sighting/137306085</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136668606</v>
+        <v>137308726</v>
       </c>
       <c r="B7" t="n">
-        <v>58860</v>
+        <v>58030</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,16 +1316,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208245</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1335,33 +1333,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skogstorp, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585009</v>
+        <v>585073</v>
       </c>
       <c r="R7" t="n">
         <v>6577320</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1385,22 +1370,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1411,67 +1396,68 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Högörtblandskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136668606</t>
+          <t>https://artportalen.se/Sighting/137308726</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136669407</v>
+        <v>136668544</v>
       </c>
       <c r="B8" t="n">
-        <v>104917</v>
+        <v>56754</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222412</v>
+        <v>206046</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1483,13 +1469,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585018</v>
+        <v>585047</v>
       </c>
       <c r="R8" t="n">
-        <v>6577342</v>
+        <v>6577324</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1518,7 +1504,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1528,7 +1514,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ko med två kalvar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1554,16 +1545,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136669407</t>
+          <t>https://artportalen.se/Sighting/136668544</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>62590568</v>
+        <v>136668377</v>
       </c>
       <c r="B9" t="n">
-        <v>101326</v>
+        <v>58860</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,37 +1562,50 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>208245</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skogstorp Ö, Srm</t>
+          <t>Skogstorp, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585112</v>
+        <v>585137</v>
       </c>
       <c r="R9" t="n">
-        <v>6577321</v>
+        <v>6577366</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1625,12 +1629,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2016-11-23</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2016-11-23</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1645,31 +1659,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Stadens biologiska mångfald (LONA)</t>
-        </is>
-      </c>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62590568</t>
+          <t>https://artportalen.se/Sighting/136668377</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136667440</v>
+        <v>136668478</v>
       </c>
       <c r="B10" t="n">
-        <v>101604</v>
+        <v>58860</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,31 +1687,32 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>208245</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1713,13 +1724,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585177</v>
+        <v>585122</v>
       </c>
       <c r="R10" t="n">
-        <v>6577418</v>
+        <v>6577337</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1748,7 +1759,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1758,12 +1769,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Växer ymnigt på skogsmarken</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1789,7 +1795,724 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136668478</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136668606</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58860</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skogstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>585009</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6577320</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136668606</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136669407</v>
+      </c>
+      <c r="B12" t="n">
+        <v>104917</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skogstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>585018</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6577342</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136669407</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>62590568</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skogstorp Ö, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>585112</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6577321</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2016-11-23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2016-11-23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Stadens biologiska mångfald (LONA)</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62590568</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136667440</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101604</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skogstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>585177</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6577418</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Växer ymnigt på skogsmarken</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136667440</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137306073</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101619</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skogstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>585085</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6577361</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137306073</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137308948</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101521</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skogstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>585089</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6577320</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Högörtblandskog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137308948</t>
         </is>
       </c>
     </row>
@@ -1804,6 +2527,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33004-2026 artfynd.xlsx
+++ b/artfynd/A 33004-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137306078</v>
       </c>
       <c r="B2" t="n">
-        <v>92958</v>
+        <v>92959</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>137312651</v>
       </c>
       <c r="B4" t="n">
-        <v>92719</v>
+        <v>92720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>137306073</v>
       </c>
       <c r="B15" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>137308948</v>
       </c>
       <c r="B16" t="n">
-        <v>101521</v>
+        <v>101522</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 33004-2026 artfynd.xlsx
+++ b/artfynd/A 33004-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137306078</v>
       </c>
       <c r="B2" t="n">
-        <v>92959</v>
+        <v>92962</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>137312651</v>
       </c>
       <c r="B4" t="n">
-        <v>92720</v>
+        <v>92723</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>137306085</v>
       </c>
       <c r="B6" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>137308726</v>
       </c>
       <c r="B7" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>137306073</v>
       </c>
       <c r="B15" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>137308948</v>
       </c>
       <c r="B16" t="n">
-        <v>101522</v>
+        <v>101527</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 33004-2026 artfynd.xlsx
+++ b/artfynd/A 33004-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137306078</v>
       </c>
       <c r="B2" t="n">
-        <v>92962</v>
+        <v>92964</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>137312651</v>
       </c>
       <c r="B4" t="n">
-        <v>92723</v>
+        <v>92725</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>137306073</v>
       </c>
       <c r="B15" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>137308948</v>
       </c>
       <c r="B16" t="n">
-        <v>101527</v>
+        <v>101530</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 33004-2026 artfynd.xlsx
+++ b/artfynd/A 33004-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137306078</v>
       </c>
       <c r="B2" t="n">
-        <v>92964</v>
+        <v>92969</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>137312651</v>
       </c>
       <c r="B4" t="n">
-        <v>92725</v>
+        <v>92730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>137306085</v>
       </c>
       <c r="B6" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>137308726</v>
       </c>
       <c r="B7" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>137306073</v>
       </c>
       <c r="B15" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>137308948</v>
       </c>
       <c r="B16" t="n">
-        <v>101530</v>
+        <v>101536</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 33004-2026 artfynd.xlsx
+++ b/artfynd/A 33004-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137306078</v>
       </c>
       <c r="B2" t="n">
-        <v>92969</v>
+        <v>92981</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>137312651</v>
       </c>
       <c r="B4" t="n">
-        <v>92730</v>
+        <v>92742</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>137306073</v>
       </c>
       <c r="B15" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>137308948</v>
       </c>
       <c r="B16" t="n">
-        <v>101536</v>
+        <v>101548</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 33004-2026 artfynd.xlsx
+++ b/artfynd/A 33004-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137306078</v>
       </c>
       <c r="B2" t="n">
-        <v>92981</v>
+        <v>92982</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>137312651</v>
       </c>
       <c r="B4" t="n">
-        <v>92742</v>
+        <v>92743</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>137306073</v>
       </c>
       <c r="B15" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>137308948</v>
       </c>
       <c r="B16" t="n">
-        <v>101548</v>
+        <v>101549</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 33004-2026 artfynd.xlsx
+++ b/artfynd/A 33004-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137306078</v>
       </c>
       <c r="B2" t="n">
-        <v>92982</v>
+        <v>92985</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>137312651</v>
       </c>
       <c r="B4" t="n">
-        <v>92743</v>
+        <v>92746</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>137306073</v>
       </c>
       <c r="B15" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>137308948</v>
       </c>
       <c r="B16" t="n">
-        <v>101549</v>
+        <v>101552</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 33004-2026 artfynd.xlsx
+++ b/artfynd/A 33004-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137306078</v>
       </c>
       <c r="B2" t="n">
-        <v>92985</v>
+        <v>92989</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>137312651</v>
       </c>
       <c r="B4" t="n">
-        <v>92746</v>
+        <v>92750</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>137306085</v>
       </c>
       <c r="B6" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>137308726</v>
       </c>
       <c r="B7" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>137306073</v>
       </c>
       <c r="B15" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>137308948</v>
       </c>
       <c r="B16" t="n">
-        <v>101552</v>
+        <v>101556</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
